--- a/authorization_forms/022_document_processing_authorization_letter_request_form--authorization_forms.xlsx
+++ b/authorization_forms/022_document_processing_authorization_letter_request_form--authorization_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>signature_method</t>
+          <t>signature_method_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Signature Method</t>
+          <t>Signature Method 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Document Types</t>
+          <t>Document Types (2)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Document ID</t>
+          <t>Document ID (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>signature_method_choices</t>
+          <t>signature_method_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>signature_method_choices</t>
+          <t>signature_method_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
